--- a/data/trans_dic/IP2002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les han extraído dientes por caries o por otro motivo</t>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 12,69</t>
+          <t>3,6; 12,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 17,03</t>
+          <t>6,56; 17,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,77</t>
+          <t>2,14; 12,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 8,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 15,45</t>
+          <t>4,67; 15,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 18,21</t>
+          <t>5,89; 18,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,78</t>
+          <t>0,82; 7,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 12,17</t>
+          <t>5,34; 11,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 15,31</t>
+          <t>7,65; 15,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,3</t>
+          <t>1,65; 7,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,59</t>
+          <t>0,65; 5,66</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,9</t>
+          <t>5,62; 10,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,0</t>
+          <t>3,39; 6,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,14</t>
+          <t>5,11; 9,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,68</t>
+          <t>3,65; 7,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,64</t>
+          <t>5,78; 9,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,11</t>
+          <t>5,2; 9,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,18</t>
+          <t>3,73; 7,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,11</t>
+          <t>2,88; 6,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,05</t>
+          <t>6,15; 9,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,35</t>
+          <t>4,8; 7,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,43</t>
+          <t>4,88; 7,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,19</t>
+          <t>3,58; 6,32</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,68</t>
+          <t>3,41; 9,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,18</t>
+          <t>1,77; 6,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 7,61</t>
+          <t>2,31; 7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 13,6</t>
+          <t>5,43; 13,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,52</t>
+          <t>2,96; 9,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 8,94</t>
+          <t>2,65; 8,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,24</t>
+          <t>2,38; 7,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 13,2</t>
+          <t>4,68; 12,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,45</t>
+          <t>3,95; 8,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,45</t>
+          <t>2,62; 6,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,88</t>
+          <t>2,75; 6,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 12,26</t>
+          <t>6,07; 11,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,91</t>
+          <t>5,52; 8,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,99</t>
+          <t>4,13; 7,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,84</t>
+          <t>4,77; 7,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,59</t>
+          <t>4,49; 7,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 8,95</t>
+          <t>5,89; 8,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,7</t>
+          <t>5,4; 8,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,27</t>
+          <t>3,73; 6,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,7</t>
+          <t>3,73; 6,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,38</t>
+          <t>6,04; 8,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,36</t>
+          <t>5,23; 7,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,56</t>
+          <t>4,54; 6,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,55</t>
+          <t>4,4; 6,63</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6393</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9770</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8639</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13896</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18409</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5368</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3175; 10962</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5825; 15202</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1205; 7207</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4822</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3865; 12656</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4868; 15668</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>550; 5372</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4591</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9129; 20417</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13104; 26578</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2035; 9681</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>740; 6424</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>29685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21174</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30575</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24195</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33934</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>32276</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23933</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>21425</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>63619</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>53451</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>54508</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>45620</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22171; 39873</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14223; 29175</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22473; 39906</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16552; 35319</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26269; 44050</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24074; 41863</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17300; 33729</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>14575; 32550</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>52223; 77467</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>42401; 66445</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>44115; 68407</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>34324; 60607</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>9743</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6965</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13319</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7768</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7809</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14872</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18185</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13496</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14774</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>28191</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5546; 15481</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2746; 10669</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3765; 12594</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8009; 19600</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4344; 13703</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4136; 13042</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4041; 13432</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8524; 23137</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>12207; 26387</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8146; 20516</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9141; 22367</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>20014; 38338</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36672</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40933</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38849</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>37518</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>95700</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>74649</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>76367</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>35622; 57038</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>27367; 47763</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31401; 52486</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29415; 50901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>40337; 61479</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>37881; 61595</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>26153; 45040</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>27882; 50173</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>80265; 110640</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>71338; 102056</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>61774; 90001</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>61650; 92894</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 12,43</t>
+          <t>3,64; 12,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 17,13</t>
+          <t>6,56; 16,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,81</t>
+          <t>2,17; 13,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,98</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 15,3</t>
+          <t>4,88; 15,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 18,96</t>
+          <t>5,99; 18,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,97</t>
+          <t>0,81; 8,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,95</t>
+          <t>5,33; 12,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,51</t>
+          <t>7,18; 14,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,83</t>
+          <t>1,99; 8,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,66</t>
+          <t>0,64; 6,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,11</t>
+          <t>5,41; 9,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,96</t>
+          <t>3,47; 7,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,07</t>
+          <t>5,14; 9,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,79</t>
+          <t>3,58; 7,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,69</t>
+          <t>5,76; 9,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,03</t>
+          <t>5,08; 9,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,27</t>
+          <t>3,66; 7,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,44</t>
+          <t>2,94; 6,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,12</t>
+          <t>6,22; 9,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,53</t>
+          <t>4,88; 7,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,57</t>
+          <t>4,89; 7,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,32</t>
+          <t>3,56; 6,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,53</t>
+          <t>3,3; 9,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,88</t>
+          <t>1,76; 6,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,74</t>
+          <t>2,14; 7,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,28</t>
+          <t>5,44; 13,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,33</t>
+          <t>3,22; 9,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,36</t>
+          <t>2,69; 8,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,91</t>
+          <t>2,17; 7,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 12,71</t>
+          <t>4,87; 13,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,53</t>
+          <t>3,8; 8,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,59</t>
+          <t>2,71; 6,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,73</t>
+          <t>2,87; 6,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,63</t>
+          <t>6,14; 11,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,84</t>
+          <t>5,64; 9,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,21</t>
+          <t>4,28; 7,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,97</t>
+          <t>4,73; 7,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,78</t>
+          <t>4,44; 7,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,98</t>
+          <t>5,78; 9,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,77</t>
+          <t>5,48; 8,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,43</t>
+          <t>3,61; 6,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,71</t>
+          <t>3,66; 6,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,32</t>
+          <t>6,1; 8,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,48</t>
+          <t>5,14; 7,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,62</t>
+          <t>4,51; 6,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,63</t>
+          <t>4,41; 6,52</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3175; 10962</t>
+          <t>3213; 10996</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5825; 15202</t>
+          <t>5824; 15079</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1205; 7207</t>
+          <t>1221; 7373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4822</t>
+          <t>0; 4716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3865; 12656</t>
+          <t>4034; 12884</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4868; 15668</t>
+          <t>4946; 15037</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>550; 5372</t>
+          <t>547; 5614</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>0; 4708</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9129; 20417</t>
+          <t>9102; 20755</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13104; 26578</t>
+          <t>12304; 25693</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2035; 9681</t>
+          <t>2464; 10035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>740; 6424</t>
+          <t>722; 7269</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22171; 39873</t>
+          <t>21321; 38311</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14223; 29175</t>
+          <t>14529; 30370</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22473; 39906</t>
+          <t>22623; 40293</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16552; 35319</t>
+          <t>16226; 35244</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26269; 44050</t>
+          <t>26184; 44234</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24074; 41863</t>
+          <t>23532; 42810</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17300; 33729</t>
+          <t>16977; 32932</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14575; 32550</t>
+          <t>14858; 32790</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52223; 77467</t>
+          <t>52794; 76409</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42401; 66445</t>
+          <t>43092; 66414</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44115; 68407</t>
+          <t>44216; 67598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34324; 60607</t>
+          <t>34159; 58551</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5546; 15481</t>
+          <t>5359; 15322</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2746; 10669</t>
+          <t>2732; 10677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3765; 12594</t>
+          <t>3481; 12855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8009; 19600</t>
+          <t>8025; 20063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4344; 13703</t>
+          <t>4733; 14200</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4136; 13042</t>
+          <t>4201; 13932</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4041; 13432</t>
+          <t>3682; 13383</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8524; 23137</t>
+          <t>8861; 24939</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12207; 26387</t>
+          <t>11766; 26048</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8146; 20516</t>
+          <t>8430; 21230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9141; 22367</t>
+          <t>9548; 22634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20014; 38338</t>
+          <t>20252; 38210</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35622; 57038</t>
+          <t>36410; 58466</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27367; 47763</t>
+          <t>28359; 47592</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31401; 52486</t>
+          <t>31165; 52117</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29415; 50901</t>
+          <t>29073; 51263</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40337; 61479</t>
+          <t>39551; 62268</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37881; 61595</t>
+          <t>38496; 61143</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26153; 45040</t>
+          <t>25286; 44593</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27882; 50173</t>
+          <t>27386; 49894</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80265; 110640</t>
+          <t>81138; 111421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71338; 102056</t>
+          <t>70205; 101380</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61774; 90001</t>
+          <t>61321; 89220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61650; 92894</t>
+          <t>61889; 91451</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,25%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,03%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,46</t>
+          <t>4,75; 15,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,99</t>
+          <t>5,39; 18,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,1</t>
+          <t>0,83; 7,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 15,58</t>
+          <t>3,61; 12,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 18,2</t>
+          <t>6,58; 17,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,33</t>
+          <t>2,25; 13,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 12,14</t>
+          <t>5,38; 12,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 14,99</t>
+          <t>7,14; 15,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,12</t>
+          <t>2,06; 8,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,4</t>
+          <t>0,68; 6,12</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,72</t>
+          <t>5,63; 9,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,25</t>
+          <t>5,06; 9,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,16</t>
+          <t>3,56; 7,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,77</t>
+          <t>2,78; 6,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,73</t>
+          <t>5,68; 9,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,24</t>
+          <t>3,54; 7,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,1</t>
+          <t>4,96; 9,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,49</t>
+          <t>3,86; 7,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,0</t>
+          <t>6,21; 9,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,53</t>
+          <t>4,75; 7,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,48</t>
+          <t>4,83; 7,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,11</t>
+          <t>3,58; 6,24</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,43</t>
+          <t>3,06; 9,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,88</t>
+          <t>2,71; 8,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,9</t>
+          <t>2,32; 8,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,6</t>
+          <t>4,81; 12,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,67</t>
+          <t>3,49; 9,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,93</t>
+          <t>1,74; 7,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,88</t>
+          <t>2,13; 7,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,7</t>
+          <t>5,99; 13,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,42</t>
+          <t>3,93; 8,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,82</t>
+          <t>2,6; 6,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,81</t>
+          <t>2,88; 6,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,59</t>
+          <t>6,15; 11,9</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,06</t>
+          <t>5,8; 8,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,18</t>
+          <t>5,47; 8,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,91</t>
+          <t>3,63; 6,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,83</t>
+          <t>3,6; 6,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,1</t>
+          <t>5,56; 8,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,71</t>
+          <t>4,12; 6,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,36</t>
+          <t>4,76; 7,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,68</t>
+          <t>4,7; 7,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,38</t>
+          <t>6,16; 8,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,43</t>
+          <t>5,22; 7,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,56</t>
+          <t>4,55; 6,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,52</t>
+          <t>4,51; 6,71</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,37 +1368,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8639</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6393</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9770</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3393</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7503</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8639</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2437</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3213; 10996</t>
+          <t>3927; 12780</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5824; 15079</t>
+          <t>4457; 15050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1221; 7373</t>
+          <t>557; 5240</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4716</t>
+          <t>0; 5673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4034; 12884</t>
+          <t>3184; 11193</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4946; 15037</t>
+          <t>5841; 15119</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>547; 5614</t>
+          <t>1264; 7746</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4708</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9102; 20755</t>
+          <t>9186; 20799</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12304; 25693</t>
+          <t>12232; 26240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2464; 10035</t>
+          <t>2545; 10264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>722; 7269</t>
+          <t>686; 6173</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33934</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32276</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23933</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19884</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29685</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21174</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>30575</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24195</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33934</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32276</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23933</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45620</t>
+          <t>43234</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21321; 38311</t>
+          <t>25599; 43850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14529; 30370</t>
+          <t>23426; 42226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22623; 40293</t>
+          <t>16515; 33278</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16226; 35244</t>
+          <t>12965; 29158</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26184; 44234</t>
+          <t>22386; 39038</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23532; 42810</t>
+          <t>14835; 29323</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16977; 32932</t>
+          <t>21824; 40201</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14858; 32790</t>
+          <t>16427; 32460</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52794; 76409</t>
+          <t>52770; 76855</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43092; 66414</t>
+          <t>41950; 64843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44216; 67598</t>
+          <t>43633; 67179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34159; 58551</t>
+          <t>32007; 55723</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7768</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7809</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13265</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>9743</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5728</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>6965</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13319</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8442</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7768</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7809</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>26904</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5359; 15322</t>
+          <t>4490; 13982</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2732; 10677</t>
+          <t>4223; 13950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3481; 12855</t>
+          <t>3935; 13985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8025; 20063</t>
+          <t>8045; 20918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4733; 14200</t>
+          <t>5675; 15729</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4201; 13932</t>
+          <t>2695; 11137</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3682; 13383</t>
+          <t>3459; 12375</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8861; 24939</t>
+          <t>8890; 20537</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11766; 26048</t>
+          <t>12170; 26140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8430; 21230</t>
+          <t>8083; 20081</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9548; 22634</t>
+          <t>9579; 22874</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20252; 38210</t>
+          <t>19400; 37557</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>45821</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>36672</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>40933</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38849</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>49879</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48684</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>72575</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36410; 58466</t>
+          <t>39689; 61267</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28359; 47592</t>
+          <t>38427; 61050</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31165; 52117</t>
+          <t>25408; 43923</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29073; 51263</t>
+          <t>24835; 46040</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39551; 62268</t>
+          <t>35874; 57442</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38496; 61143</t>
+          <t>27318; 46356</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25286; 44593</t>
+          <t>31333; 51664</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27386; 49894</t>
+          <t>29150; 48865</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81138; 111421</t>
+          <t>81872; 111457</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70205; 101380</t>
+          <t>71185; 100463</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61321; 89220</t>
+          <t>61818; 89187</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61889; 91451</t>
+          <t>59116; 87880</t>
         </is>
       </c>
     </row>
